--- a/experiment/test/results-Urban100/Urban100.xlsx
+++ b/experiment/test/results-Urban100/Urban100.xlsx
@@ -452,10 +452,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>27.98</v>
+        <v>29.27</v>
       </c>
       <c r="C2" t="n">
-        <v>0.7762</v>
+        <v>0.8245</v>
       </c>
     </row>
     <row r="3">
@@ -465,10 +465,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>27.2</v>
+        <v>29.04</v>
       </c>
       <c r="C3" t="n">
-        <v>0.8345</v>
+        <v>0.8882</v>
       </c>
     </row>
     <row r="4">
@@ -478,10 +478,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>24.13</v>
+        <v>25.47</v>
       </c>
       <c r="C4" t="n">
-        <v>0.7038</v>
+        <v>0.7846</v>
       </c>
     </row>
     <row r="5">
@@ -491,10 +491,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>23.73</v>
+        <v>25.61</v>
       </c>
       <c r="C5" t="n">
-        <v>0.8532</v>
+        <v>0.9016</v>
       </c>
     </row>
     <row r="6">
@@ -504,10 +504,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>29.05</v>
+        <v>31.33</v>
       </c>
       <c r="C6" t="n">
-        <v>0.9586</v>
+        <v>0.9715</v>
       </c>
     </row>
     <row r="7">
@@ -517,10 +517,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>22.8</v>
+        <v>23.96</v>
       </c>
       <c r="C7" t="n">
-        <v>0.641</v>
+        <v>0.7048</v>
       </c>
     </row>
     <row r="8">
@@ -530,10 +530,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>29.86</v>
+        <v>32.08</v>
       </c>
       <c r="C8" t="n">
-        <v>0.8685</v>
+        <v>0.9177999999999999</v>
       </c>
     </row>
     <row r="9">
@@ -543,10 +543,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>21.84</v>
+        <v>23.44</v>
       </c>
       <c r="C9" t="n">
-        <v>0.6895</v>
+        <v>0.7833</v>
       </c>
     </row>
     <row r="10">
@@ -556,10 +556,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>34.59</v>
+        <v>36.23</v>
       </c>
       <c r="C10" t="n">
-        <v>0.9360000000000001</v>
+        <v>0.9520999999999999</v>
       </c>
     </row>
     <row r="11">
@@ -569,10 +569,10 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>27.95</v>
+        <v>29.59</v>
       </c>
       <c r="C11" t="n">
-        <v>0.9004</v>
+        <v>0.9266</v>
       </c>
     </row>
     <row r="12">
@@ -582,10 +582,10 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>18.45</v>
+        <v>20.73</v>
       </c>
       <c r="C12" t="n">
-        <v>0.8144</v>
+        <v>0.8771</v>
       </c>
     </row>
     <row r="13">
@@ -595,10 +595,10 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>24.15</v>
+        <v>25.41</v>
       </c>
       <c r="C13" t="n">
-        <v>0.7527</v>
+        <v>0.8192</v>
       </c>
     </row>
     <row r="14">
@@ -608,10 +608,10 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>29.92</v>
+        <v>31.35</v>
       </c>
       <c r="C14" t="n">
-        <v>0.8492</v>
+        <v>0.8871</v>
       </c>
     </row>
     <row r="15">
@@ -621,10 +621,10 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>22.58</v>
+        <v>23.47</v>
       </c>
       <c r="C15" t="n">
-        <v>0.7050999999999999</v>
+        <v>0.7642</v>
       </c>
     </row>
     <row r="16">
@@ -634,10 +634,10 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>26.5</v>
+        <v>27.78</v>
       </c>
       <c r="C16" t="n">
-        <v>0.747</v>
+        <v>0.7866</v>
       </c>
     </row>
     <row r="17">
@@ -647,10 +647,10 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>31.37</v>
+        <v>33.13</v>
       </c>
       <c r="C17" t="n">
-        <v>0.924</v>
+        <v>0.9387</v>
       </c>
     </row>
     <row r="18">
@@ -660,10 +660,10 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>26.14</v>
+        <v>27.83</v>
       </c>
       <c r="C18" t="n">
-        <v>0.8414</v>
+        <v>0.8935999999999999</v>
       </c>
     </row>
     <row r="19">
@@ -673,10 +673,10 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>26.46</v>
+        <v>27.61</v>
       </c>
       <c r="C19" t="n">
-        <v>0.7207</v>
+        <v>0.7902</v>
       </c>
     </row>
     <row r="20">
@@ -686,10 +686,10 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>22.71</v>
+        <v>24.54</v>
       </c>
       <c r="C20" t="n">
-        <v>0.8326</v>
+        <v>0.8824</v>
       </c>
     </row>
     <row r="21">
@@ -699,10 +699,10 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>22.34</v>
+        <v>24.01</v>
       </c>
       <c r="C21" t="n">
-        <v>0.7322</v>
+        <v>0.8106</v>
       </c>
     </row>
     <row r="22">
@@ -712,10 +712,10 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>30.04</v>
+        <v>31.47</v>
       </c>
       <c r="C22" t="n">
-        <v>0.7927</v>
+        <v>0.8423</v>
       </c>
     </row>
     <row r="23">
@@ -725,10 +725,10 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>26.2</v>
+        <v>27.31</v>
       </c>
       <c r="C23" t="n">
-        <v>0.7674</v>
+        <v>0.8198</v>
       </c>
     </row>
     <row r="24">
@@ -738,10 +738,10 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>30.96</v>
+        <v>33.4</v>
       </c>
       <c r="C24" t="n">
-        <v>0.9238</v>
+        <v>0.9540999999999999</v>
       </c>
     </row>
     <row r="25">
@@ -751,10 +751,10 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>21.26</v>
+        <v>22.89</v>
       </c>
       <c r="C25" t="n">
-        <v>0.7111</v>
+        <v>0.7855</v>
       </c>
     </row>
     <row r="26">
@@ -764,10 +764,10 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>32.57</v>
+        <v>34.04</v>
       </c>
       <c r="C26" t="n">
-        <v>0.9082</v>
+        <v>0.9295</v>
       </c>
     </row>
     <row r="27">
@@ -777,10 +777,10 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>28.51</v>
+        <v>29.37</v>
       </c>
       <c r="C27" t="n">
-        <v>0.7175</v>
+        <v>0.7416</v>
       </c>
     </row>
     <row r="28">
@@ -790,10 +790,10 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>28.66</v>
+        <v>29.73</v>
       </c>
       <c r="C28" t="n">
-        <v>0.8074</v>
+        <v>0.8496</v>
       </c>
     </row>
     <row r="29">
@@ -803,10 +803,10 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>31.83</v>
+        <v>33.77</v>
       </c>
       <c r="C29" t="n">
-        <v>0.8836000000000001</v>
+        <v>0.9121</v>
       </c>
     </row>
     <row r="30">
@@ -816,10 +816,10 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>27.68</v>
+        <v>29.46</v>
       </c>
       <c r="C30" t="n">
-        <v>0.8814</v>
+        <v>0.9179</v>
       </c>
     </row>
     <row r="31">
@@ -829,10 +829,10 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>25.24</v>
+        <v>27.42</v>
       </c>
       <c r="C31" t="n">
-        <v>0.834</v>
+        <v>0.8972</v>
       </c>
     </row>
     <row r="32">
@@ -842,10 +842,10 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>24.45</v>
+        <v>25.92</v>
       </c>
       <c r="C32" t="n">
-        <v>0.802</v>
+        <v>0.863</v>
       </c>
     </row>
     <row r="33">
@@ -855,10 +855,10 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>29.59</v>
+        <v>31.29</v>
       </c>
       <c r="C33" t="n">
-        <v>0.8694</v>
+        <v>0.9096</v>
       </c>
     </row>
     <row r="34">
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>27.87</v>
+        <v>29.19</v>
       </c>
       <c r="C34" t="n">
-        <v>0.8260999999999999</v>
+        <v>0.8723</v>
       </c>
     </row>
     <row r="35">
@@ -881,10 +881,10 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>23.3</v>
+        <v>24.4</v>
       </c>
       <c r="C35" t="n">
-        <v>0.5969</v>
+        <v>0.6711</v>
       </c>
     </row>
     <row r="36">
@@ -894,10 +894,10 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>29.73</v>
+        <v>31.16</v>
       </c>
       <c r="C36" t="n">
-        <v>0.8907</v>
+        <v>0.9161</v>
       </c>
     </row>
     <row r="37">
@@ -907,10 +907,10 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>29.09</v>
+        <v>30.84</v>
       </c>
       <c r="C37" t="n">
-        <v>0.8912</v>
+        <v>0.924</v>
       </c>
     </row>
     <row r="38">
@@ -920,10 +920,10 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>26.69</v>
+        <v>29.2</v>
       </c>
       <c r="C38" t="n">
-        <v>0.8088</v>
+        <v>0.8814</v>
       </c>
     </row>
     <row r="39">
@@ -933,10 +933,10 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>27.42</v>
+        <v>28.88</v>
       </c>
       <c r="C39" t="n">
-        <v>0.7038</v>
+        <v>0.7762</v>
       </c>
     </row>
     <row r="40">
@@ -946,10 +946,10 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>23.48</v>
+        <v>25.07</v>
       </c>
       <c r="C40" t="n">
-        <v>0.7702</v>
+        <v>0.8385</v>
       </c>
     </row>
     <row r="41">
@@ -959,10 +959,10 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>27.71</v>
+        <v>30.12</v>
       </c>
       <c r="C41" t="n">
-        <v>0.9488</v>
+        <v>0.9643</v>
       </c>
     </row>
     <row r="42">
@@ -972,10 +972,10 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>27.22</v>
+        <v>29.66</v>
       </c>
       <c r="C42" t="n">
-        <v>0.8985</v>
+        <v>0.9334</v>
       </c>
     </row>
     <row r="43">
@@ -985,10 +985,10 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>29.28</v>
+        <v>31.24</v>
       </c>
       <c r="C43" t="n">
-        <v>0.8951</v>
+        <v>0.9286</v>
       </c>
     </row>
     <row r="44">
@@ -998,10 +998,10 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>33.09</v>
+        <v>34.25</v>
       </c>
       <c r="C44" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.9529</v>
       </c>
     </row>
     <row r="45">
@@ -1011,10 +1011,10 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>32.92</v>
+        <v>35.29</v>
       </c>
       <c r="C45" t="n">
-        <v>0.8888</v>
+        <v>0.9353</v>
       </c>
     </row>
     <row r="46">
@@ -1024,10 +1024,10 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>24.05</v>
+        <v>27.15</v>
       </c>
       <c r="C46" t="n">
-        <v>0.7332</v>
+        <v>0.8446</v>
       </c>
     </row>
     <row r="47">
@@ -1037,10 +1037,10 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>23.93</v>
+        <v>25.12</v>
       </c>
       <c r="C47" t="n">
-        <v>0.7754</v>
+        <v>0.8395</v>
       </c>
     </row>
     <row r="48">
@@ -1050,10 +1050,10 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>22.38</v>
+        <v>23.85</v>
       </c>
       <c r="C48" t="n">
-        <v>0.7973</v>
+        <v>0.8586</v>
       </c>
     </row>
     <row r="49">
@@ -1063,10 +1063,10 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>20.9</v>
+        <v>22.75</v>
       </c>
       <c r="C49" t="n">
-        <v>0.8366</v>
+        <v>0.8927</v>
       </c>
     </row>
     <row r="50">
@@ -1076,10 +1076,10 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>23.95</v>
+        <v>25.66</v>
       </c>
       <c r="C50" t="n">
-        <v>0.7688</v>
+        <v>0.8335</v>
       </c>
     </row>
     <row r="51">
@@ -1089,10 +1089,10 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>25.56</v>
+        <v>27.17</v>
       </c>
       <c r="C51" t="n">
-        <v>0.7885</v>
+        <v>0.8496</v>
       </c>
     </row>
     <row r="52">
@@ -1102,10 +1102,10 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>27.73</v>
+        <v>29.84</v>
       </c>
       <c r="C52" t="n">
-        <v>0.8583</v>
+        <v>0.9084</v>
       </c>
     </row>
     <row r="53">
@@ -1115,10 +1115,10 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>29.49</v>
+        <v>31.12</v>
       </c>
       <c r="C53" t="n">
-        <v>0.9177999999999999</v>
+        <v>0.9398</v>
       </c>
     </row>
     <row r="54">
@@ -1128,10 +1128,10 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>22.75</v>
+        <v>24.4</v>
       </c>
       <c r="C54" t="n">
-        <v>0.7467</v>
+        <v>0.8228</v>
       </c>
     </row>
     <row r="55">
@@ -1141,10 +1141,10 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>21.46</v>
+        <v>22.59</v>
       </c>
       <c r="C55" t="n">
-        <v>0.6704</v>
+        <v>0.7429</v>
       </c>
     </row>
     <row r="56">
@@ -1154,10 +1154,10 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>32.87</v>
+        <v>34.39</v>
       </c>
       <c r="C56" t="n">
-        <v>0.949</v>
+        <v>0.961</v>
       </c>
     </row>
     <row r="57">
@@ -1167,10 +1167,10 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>25.39</v>
+        <v>27.26</v>
       </c>
       <c r="C57" t="n">
-        <v>0.7999000000000001</v>
+        <v>0.8659</v>
       </c>
     </row>
     <row r="58">
@@ -1180,10 +1180,10 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>31.81</v>
+        <v>33.66</v>
       </c>
       <c r="C58" t="n">
-        <v>0.9121</v>
+        <v>0.9399999999999999</v>
       </c>
     </row>
     <row r="59">
@@ -1193,10 +1193,10 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>26.53</v>
+        <v>28.85</v>
       </c>
       <c r="C59" t="n">
-        <v>0.8777</v>
+        <v>0.9242</v>
       </c>
     </row>
     <row r="60">
@@ -1206,10 +1206,10 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>22.91</v>
+        <v>24.68</v>
       </c>
       <c r="C60" t="n">
-        <v>0.7905</v>
+        <v>0.8418</v>
       </c>
     </row>
     <row r="61">
@@ -1219,10 +1219,10 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>22.78</v>
+        <v>23.72</v>
       </c>
       <c r="C61" t="n">
-        <v>0.5867</v>
+        <v>0.6703</v>
       </c>
     </row>
     <row r="62">
@@ -1232,10 +1232,10 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>25.14</v>
+        <v>26.74</v>
       </c>
       <c r="C62" t="n">
-        <v>0.7778</v>
+        <v>0.8452</v>
       </c>
     </row>
     <row r="63">
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="B63" t="n">
-        <v>22.73</v>
+        <v>24.9</v>
       </c>
       <c r="C63" t="n">
-        <v>0.846</v>
+        <v>0.9055</v>
       </c>
     </row>
     <row r="64">
@@ -1258,10 +1258,10 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>22.61</v>
+        <v>23.75</v>
       </c>
       <c r="C64" t="n">
-        <v>0.6271</v>
+        <v>0.6712</v>
       </c>
     </row>
     <row r="65">
@@ -1271,10 +1271,10 @@
         </is>
       </c>
       <c r="B65" t="n">
-        <v>26.84</v>
+        <v>28.72</v>
       </c>
       <c r="C65" t="n">
-        <v>0.7948</v>
+        <v>0.8596</v>
       </c>
     </row>
     <row r="66">
@@ -1284,10 +1284,10 @@
         </is>
       </c>
       <c r="B66" t="n">
-        <v>25.67</v>
+        <v>27.51</v>
       </c>
       <c r="C66" t="n">
-        <v>0.7392</v>
+        <v>0.8329</v>
       </c>
     </row>
     <row r="67">
@@ -1297,10 +1297,10 @@
         </is>
       </c>
       <c r="B67" t="n">
-        <v>22.3</v>
+        <v>23.4</v>
       </c>
       <c r="C67" t="n">
-        <v>0.6487000000000001</v>
+        <v>0.7313</v>
       </c>
     </row>
     <row r="68">
@@ -1310,10 +1310,10 @@
         </is>
       </c>
       <c r="B68" t="n">
-        <v>20.58</v>
+        <v>22.3</v>
       </c>
       <c r="C68" t="n">
-        <v>0.8994</v>
+        <v>0.9272</v>
       </c>
     </row>
     <row r="69">
@@ -1323,10 +1323,10 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>30.95</v>
+        <v>33.35</v>
       </c>
       <c r="C69" t="n">
-        <v>0.8988</v>
+        <v>0.9379999999999999</v>
       </c>
     </row>
     <row r="70">
@@ -1336,10 +1336,10 @@
         </is>
       </c>
       <c r="B70" t="n">
-        <v>25.04</v>
+        <v>26.31</v>
       </c>
       <c r="C70" t="n">
-        <v>0.7669</v>
+        <v>0.8276</v>
       </c>
     </row>
     <row r="71">
@@ -1349,10 +1349,10 @@
         </is>
       </c>
       <c r="B71" t="n">
-        <v>22.24</v>
+        <v>23.08</v>
       </c>
       <c r="C71" t="n">
-        <v>0.6038</v>
+        <v>0.6745</v>
       </c>
     </row>
     <row r="72">
@@ -1362,10 +1362,10 @@
         </is>
       </c>
       <c r="B72" t="n">
-        <v>28.42</v>
+        <v>29.57</v>
       </c>
       <c r="C72" t="n">
-        <v>0.6836</v>
+        <v>0.7483</v>
       </c>
     </row>
     <row r="73">
@@ -1375,10 +1375,10 @@
         </is>
       </c>
       <c r="B73" t="n">
-        <v>20.83</v>
+        <v>22.63</v>
       </c>
       <c r="C73" t="n">
-        <v>0.8444</v>
+        <v>0.8944</v>
       </c>
     </row>
     <row r="74">
@@ -1388,10 +1388,10 @@
         </is>
       </c>
       <c r="B74" t="n">
-        <v>20.37</v>
+        <v>22.85</v>
       </c>
       <c r="C74" t="n">
-        <v>0.5965</v>
+        <v>0.7326</v>
       </c>
     </row>
     <row r="75">
@@ -1401,10 +1401,10 @@
         </is>
       </c>
       <c r="B75" t="n">
-        <v>24.16</v>
+        <v>25.63</v>
       </c>
       <c r="C75" t="n">
-        <v>0.7415</v>
+        <v>0.8157</v>
       </c>
     </row>
     <row r="76">
@@ -1414,10 +1414,10 @@
         </is>
       </c>
       <c r="B76" t="n">
-        <v>32.25</v>
+        <v>33.66</v>
       </c>
       <c r="C76" t="n">
-        <v>0.8934</v>
+        <v>0.9123</v>
       </c>
     </row>
     <row r="77">
@@ -1427,10 +1427,10 @@
         </is>
       </c>
       <c r="B77" t="n">
-        <v>23.64</v>
+        <v>26.46</v>
       </c>
       <c r="C77" t="n">
-        <v>0.7613</v>
+        <v>0.8717</v>
       </c>
     </row>
     <row r="78">
@@ -1440,10 +1440,10 @@
         </is>
       </c>
       <c r="B78" t="n">
-        <v>22.8</v>
+        <v>23.81</v>
       </c>
       <c r="C78" t="n">
-        <v>0.6818</v>
+        <v>0.7558</v>
       </c>
     </row>
     <row r="79">
@@ -1453,10 +1453,10 @@
         </is>
       </c>
       <c r="B79" t="n">
-        <v>27.95</v>
+        <v>29.52</v>
       </c>
       <c r="C79" t="n">
-        <v>0.789</v>
+        <v>0.8425</v>
       </c>
     </row>
     <row r="80">
@@ -1466,10 +1466,10 @@
         </is>
       </c>
       <c r="B80" t="n">
-        <v>25.69</v>
+        <v>27.21</v>
       </c>
       <c r="C80" t="n">
-        <v>0.7086</v>
+        <v>0.7801</v>
       </c>
     </row>
     <row r="81">
@@ -1479,10 +1479,10 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>35.92</v>
+        <v>37.41</v>
       </c>
       <c r="C81" t="n">
-        <v>0.9565</v>
+        <v>0.9676</v>
       </c>
     </row>
     <row r="82">
@@ -1492,10 +1492,10 @@
         </is>
       </c>
       <c r="B82" t="n">
-        <v>38.2</v>
+        <v>39.99</v>
       </c>
       <c r="C82" t="n">
-        <v>0.9758</v>
+        <v>0.9815</v>
       </c>
     </row>
     <row r="83">
@@ -1505,10 +1505,10 @@
         </is>
       </c>
       <c r="B83" t="n">
-        <v>33.71</v>
+        <v>35.3</v>
       </c>
       <c r="C83" t="n">
-        <v>0.946</v>
+        <v>0.9579</v>
       </c>
     </row>
     <row r="84">
@@ -1518,10 +1518,10 @@
         </is>
       </c>
       <c r="B84" t="n">
-        <v>22.54</v>
+        <v>23.82</v>
       </c>
       <c r="C84" t="n">
-        <v>0.7208</v>
+        <v>0.7929</v>
       </c>
     </row>
     <row r="85">
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="B85" t="n">
-        <v>29.07</v>
+        <v>30.9</v>
       </c>
       <c r="C85" t="n">
-        <v>0.8233</v>
+        <v>0.8768</v>
       </c>
     </row>
     <row r="86">
@@ -1544,10 +1544,10 @@
         </is>
       </c>
       <c r="B86" t="n">
-        <v>28.63</v>
+        <v>30.72</v>
       </c>
       <c r="C86" t="n">
-        <v>0.9094</v>
+        <v>0.9426</v>
       </c>
     </row>
     <row r="87">
@@ -1557,10 +1557,10 @@
         </is>
       </c>
       <c r="B87" t="n">
-        <v>30.65</v>
+        <v>32.64</v>
       </c>
       <c r="C87" t="n">
-        <v>0.8909</v>
+        <v>0.9212</v>
       </c>
     </row>
     <row r="88">
@@ -1570,10 +1570,10 @@
         </is>
       </c>
       <c r="B88" t="n">
-        <v>28.72</v>
+        <v>30.39</v>
       </c>
       <c r="C88" t="n">
-        <v>0.9023</v>
+        <v>0.9304</v>
       </c>
     </row>
     <row r="89">
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="B89" t="n">
-        <v>20.01</v>
+        <v>21.41</v>
       </c>
       <c r="C89" t="n">
-        <v>0.5858</v>
+        <v>0.6967</v>
       </c>
     </row>
     <row r="90">
@@ -1596,10 +1596,10 @@
         </is>
       </c>
       <c r="B90" t="n">
-        <v>26.92</v>
+        <v>28.39</v>
       </c>
       <c r="C90" t="n">
-        <v>0.7295</v>
+        <v>0.8046</v>
       </c>
     </row>
     <row r="91">
@@ -1609,10 +1609,10 @@
         </is>
       </c>
       <c r="B91" t="n">
-        <v>39.13</v>
+        <v>41.47</v>
       </c>
       <c r="C91" t="n">
-        <v>0.979</v>
+        <v>0.9852</v>
       </c>
     </row>
     <row r="92">
@@ -1622,10 +1622,10 @@
         </is>
       </c>
       <c r="B92" t="n">
-        <v>24.23</v>
+        <v>25.89</v>
       </c>
       <c r="C92" t="n">
-        <v>0.7007</v>
+        <v>0.7929</v>
       </c>
     </row>
     <row r="93">
@@ -1635,10 +1635,10 @@
         </is>
       </c>
       <c r="B93" t="n">
-        <v>19.32</v>
+        <v>20.56</v>
       </c>
       <c r="C93" t="n">
-        <v>0.6772</v>
+        <v>0.7392</v>
       </c>
     </row>
     <row r="94">
@@ -1648,10 +1648,10 @@
         </is>
       </c>
       <c r="B94" t="n">
-        <v>30.05</v>
+        <v>32.69</v>
       </c>
       <c r="C94" t="n">
-        <v>0.9351</v>
+        <v>0.9553</v>
       </c>
     </row>
     <row r="95">
@@ -1661,10 +1661,10 @@
         </is>
       </c>
       <c r="B95" t="n">
-        <v>27.45</v>
+        <v>28.64</v>
       </c>
       <c r="C95" t="n">
-        <v>0.7946</v>
+        <v>0.8409</v>
       </c>
     </row>
     <row r="96">
@@ -1674,10 +1674,10 @@
         </is>
       </c>
       <c r="B96" t="n">
-        <v>20.37</v>
+        <v>21.45</v>
       </c>
       <c r="C96" t="n">
-        <v>0.4744</v>
+        <v>0.5809</v>
       </c>
     </row>
     <row r="97">
@@ -1687,10 +1687,10 @@
         </is>
       </c>
       <c r="B97" t="n">
-        <v>25.83</v>
+        <v>28.09</v>
       </c>
       <c r="C97" t="n">
-        <v>0.8853</v>
+        <v>0.9219000000000001</v>
       </c>
     </row>
     <row r="98">
@@ -1700,10 +1700,10 @@
         </is>
       </c>
       <c r="B98" t="n">
-        <v>25.18</v>
+        <v>26.68</v>
       </c>
       <c r="C98" t="n">
-        <v>0.7774</v>
+        <v>0.8391</v>
       </c>
     </row>
     <row r="99">
@@ -1713,10 +1713,10 @@
         </is>
       </c>
       <c r="B99" t="n">
-        <v>20.89</v>
+        <v>21.93</v>
       </c>
       <c r="C99" t="n">
-        <v>0.5495</v>
+        <v>0.65</v>
       </c>
     </row>
     <row r="100">
@@ -1726,10 +1726,10 @@
         </is>
       </c>
       <c r="B100" t="n">
-        <v>26.52</v>
+        <v>28.47</v>
       </c>
       <c r="C100" t="n">
-        <v>0.8232</v>
+        <v>0.8781</v>
       </c>
     </row>
     <row r="101">
@@ -1739,10 +1739,10 @@
         </is>
       </c>
       <c r="B101" t="n">
-        <v>26.69</v>
+        <v>27.39</v>
       </c>
       <c r="C101" t="n">
-        <v>0.7613</v>
+        <v>0.7833</v>
       </c>
     </row>
     <row r="102">
@@ -1752,10 +1752,10 @@
         </is>
       </c>
       <c r="B102" t="n">
-        <v>26.49</v>
+        <v>28.15</v>
       </c>
       <c r="C102" t="n">
-        <v>0.7995</v>
+        <v>0.8526</v>
       </c>
     </row>
   </sheetData>

--- a/experiment/test/results-Urban100/Urban100.xlsx
+++ b/experiment/test/results-Urban100/Urban100.xlsx
@@ -452,10 +452,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>27.78</v>
+        <v>27.55</v>
       </c>
       <c r="C2" t="n">
-        <v>0.7719</v>
+        <v>0.7662</v>
       </c>
     </row>
     <row r="3">
@@ -465,10 +465,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>26.99</v>
+        <v>26.68</v>
       </c>
       <c r="C3" t="n">
-        <v>0.8253</v>
+        <v>0.8172</v>
       </c>
     </row>
     <row r="4">
@@ -478,10 +478,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>24.07</v>
+        <v>23.9</v>
       </c>
       <c r="C4" t="n">
-        <v>0.6979</v>
+        <v>0.6869</v>
       </c>
     </row>
     <row r="5">
@@ -491,10 +491,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>23.2</v>
+        <v>23.01</v>
       </c>
       <c r="C5" t="n">
-        <v>0.8352000000000001</v>
+        <v>0.8286</v>
       </c>
     </row>
     <row r="6">
@@ -504,10 +504,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>28.46</v>
+        <v>28.04</v>
       </c>
       <c r="C6" t="n">
-        <v>0.9529</v>
+        <v>0.9498</v>
       </c>
     </row>
     <row r="7">
@@ -517,10 +517,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>22.69</v>
+        <v>22.52</v>
       </c>
       <c r="C7" t="n">
-        <v>0.6353</v>
+        <v>0.6281</v>
       </c>
     </row>
     <row r="8">
@@ -530,10 +530,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>29.74</v>
+        <v>29.57</v>
       </c>
       <c r="C8" t="n">
-        <v>0.866</v>
+        <v>0.8621</v>
       </c>
     </row>
     <row r="9">
@@ -543,10 +543,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>21.72</v>
+        <v>21.57</v>
       </c>
       <c r="C9" t="n">
-        <v>0.6771</v>
+        <v>0.6671</v>
       </c>
     </row>
     <row r="10">
@@ -556,10 +556,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>34.34</v>
+        <v>33.96</v>
       </c>
       <c r="C10" t="n">
-        <v>0.9324</v>
+        <v>0.9272</v>
       </c>
     </row>
     <row r="11">
@@ -569,10 +569,10 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>27.67</v>
+        <v>27.39</v>
       </c>
       <c r="C11" t="n">
-        <v>0.8938</v>
+        <v>0.8897</v>
       </c>
     </row>
     <row r="12">
@@ -582,10 +582,10 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>17.91</v>
+        <v>17.62</v>
       </c>
       <c r="C12" t="n">
-        <v>0.7923</v>
+        <v>0.7764</v>
       </c>
     </row>
     <row r="13">
@@ -595,10 +595,10 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>24.18</v>
+        <v>23.94</v>
       </c>
       <c r="C13" t="n">
-        <v>0.7509</v>
+        <v>0.7359</v>
       </c>
     </row>
     <row r="14">
@@ -608,10 +608,10 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>29.82</v>
+        <v>29.64</v>
       </c>
       <c r="C14" t="n">
-        <v>0.8458</v>
+        <v>0.841</v>
       </c>
     </row>
     <row r="15">
@@ -621,10 +621,10 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>22.52</v>
+        <v>22.41</v>
       </c>
       <c r="C15" t="n">
-        <v>0.6974</v>
+        <v>0.6888</v>
       </c>
     </row>
     <row r="16">
@@ -634,10 +634,10 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>26.37</v>
+        <v>26.17</v>
       </c>
       <c r="C16" t="n">
-        <v>0.7432</v>
+        <v>0.7368</v>
       </c>
     </row>
     <row r="17">
@@ -647,10 +647,10 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>31.08</v>
+        <v>30.28</v>
       </c>
       <c r="C17" t="n">
-        <v>0.9198</v>
+        <v>0.9134</v>
       </c>
     </row>
     <row r="18">
@@ -660,10 +660,10 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>26</v>
+        <v>25.84</v>
       </c>
       <c r="C18" t="n">
-        <v>0.8363</v>
+        <v>0.8306</v>
       </c>
     </row>
     <row r="19">
@@ -673,10 +673,10 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>26.47</v>
+        <v>26.4</v>
       </c>
       <c r="C19" t="n">
-        <v>0.72</v>
+        <v>0.7161</v>
       </c>
     </row>
     <row r="20">
@@ -686,10 +686,10 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>22.65</v>
+        <v>22.03</v>
       </c>
       <c r="C20" t="n">
-        <v>0.8262</v>
+        <v>0.8115</v>
       </c>
     </row>
     <row r="21">
@@ -699,10 +699,10 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>22.33</v>
+        <v>22.13</v>
       </c>
       <c r="C21" t="n">
-        <v>0.7267</v>
+        <v>0.7204</v>
       </c>
     </row>
     <row r="22">
@@ -712,10 +712,10 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>29.91</v>
+        <v>29.78</v>
       </c>
       <c r="C22" t="n">
-        <v>0.7897</v>
+        <v>0.786</v>
       </c>
     </row>
     <row r="23">
@@ -725,10 +725,10 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>26.18</v>
+        <v>26.09</v>
       </c>
       <c r="C23" t="n">
-        <v>0.7648</v>
+        <v>0.7601</v>
       </c>
     </row>
     <row r="24">
@@ -738,10 +738,10 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>30.95</v>
+        <v>30.76</v>
       </c>
       <c r="C24" t="n">
-        <v>0.9233</v>
+        <v>0.9208</v>
       </c>
     </row>
     <row r="25">
@@ -751,10 +751,10 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>21.05</v>
+        <v>20.2</v>
       </c>
       <c r="C25" t="n">
-        <v>0.6997</v>
+        <v>0.6572</v>
       </c>
     </row>
     <row r="26">
@@ -764,10 +764,10 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>32.18</v>
+        <v>31.92</v>
       </c>
       <c r="C26" t="n">
-        <v>0.903</v>
+        <v>0.9003</v>
       </c>
     </row>
     <row r="27">
@@ -777,10 +777,10 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>28.15</v>
+        <v>27.65</v>
       </c>
       <c r="C27" t="n">
-        <v>0.707</v>
+        <v>0.6932</v>
       </c>
     </row>
     <row r="28">
@@ -790,10 +790,10 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>28.55</v>
+        <v>28.24</v>
       </c>
       <c r="C28" t="n">
-        <v>0.8033</v>
+        <v>0.7936</v>
       </c>
     </row>
     <row r="29">
@@ -803,10 +803,10 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>31.8</v>
+        <v>31.44</v>
       </c>
       <c r="C29" t="n">
-        <v>0.8812</v>
+        <v>0.8766</v>
       </c>
     </row>
     <row r="30">
@@ -816,10 +816,10 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>27.53</v>
+        <v>26.94</v>
       </c>
       <c r="C30" t="n">
-        <v>0.8752</v>
+        <v>0.8627</v>
       </c>
     </row>
     <row r="31">
@@ -829,10 +829,10 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>25.13</v>
+        <v>24.81</v>
       </c>
       <c r="C31" t="n">
-        <v>0.8266</v>
+        <v>0.8141</v>
       </c>
     </row>
     <row r="32">
@@ -842,10 +842,10 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>24.39</v>
+        <v>24.29</v>
       </c>
       <c r="C32" t="n">
-        <v>0.7969000000000001</v>
+        <v>0.7937</v>
       </c>
     </row>
     <row r="33">
@@ -855,10 +855,10 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>29.45</v>
+        <v>29.21</v>
       </c>
       <c r="C33" t="n">
-        <v>0.8628</v>
+        <v>0.8555</v>
       </c>
     </row>
     <row r="34">
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>27.72</v>
+        <v>27.12</v>
       </c>
       <c r="C34" t="n">
-        <v>0.8199</v>
+        <v>0.7982</v>
       </c>
     </row>
     <row r="35">
@@ -881,10 +881,10 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>23.24</v>
+        <v>23.1</v>
       </c>
       <c r="C35" t="n">
-        <v>0.5945</v>
+        <v>0.5873</v>
       </c>
     </row>
     <row r="36">
@@ -894,10 +894,10 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>29.53</v>
+        <v>29.07</v>
       </c>
       <c r="C36" t="n">
-        <v>0.8846000000000001</v>
+        <v>0.8746</v>
       </c>
     </row>
     <row r="37">
@@ -907,10 +907,10 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>29.07</v>
+        <v>28.97</v>
       </c>
       <c r="C37" t="n">
-        <v>0.8901</v>
+        <v>0.8873</v>
       </c>
     </row>
     <row r="38">
@@ -920,10 +920,10 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>26.79</v>
+        <v>26.56</v>
       </c>
       <c r="C38" t="n">
-        <v>0.8081</v>
+        <v>0.8026</v>
       </c>
     </row>
     <row r="39">
@@ -933,10 +933,10 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>27.38</v>
+        <v>27.04</v>
       </c>
       <c r="C39" t="n">
-        <v>0.6999</v>
+        <v>0.6793</v>
       </c>
     </row>
     <row r="40">
@@ -946,10 +946,10 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>23.32</v>
+        <v>23</v>
       </c>
       <c r="C40" t="n">
-        <v>0.7605</v>
+        <v>0.7419</v>
       </c>
     </row>
     <row r="41">
@@ -959,10 +959,10 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>27.39</v>
+        <v>27.44</v>
       </c>
       <c r="C41" t="n">
-        <v>0.9415</v>
+        <v>0.9412</v>
       </c>
     </row>
     <row r="42">
@@ -972,10 +972,10 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>26.78</v>
+        <v>26.48</v>
       </c>
       <c r="C42" t="n">
-        <v>0.8882</v>
+        <v>0.8832</v>
       </c>
     </row>
     <row r="43">
@@ -985,10 +985,10 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>29.18</v>
+        <v>28.9</v>
       </c>
       <c r="C43" t="n">
-        <v>0.8917</v>
+        <v>0.8871</v>
       </c>
     </row>
     <row r="44">
@@ -998,10 +998,10 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>32.36</v>
+        <v>31.81</v>
       </c>
       <c r="C44" t="n">
-        <v>0.9340000000000001</v>
+        <v>0.9325</v>
       </c>
     </row>
     <row r="45">
@@ -1011,10 +1011,10 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>32.32</v>
+        <v>32.09</v>
       </c>
       <c r="C45" t="n">
-        <v>0.8835</v>
+        <v>0.8671</v>
       </c>
     </row>
     <row r="46">
@@ -1024,10 +1024,10 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>23.89</v>
+        <v>23.08</v>
       </c>
       <c r="C46" t="n">
-        <v>0.721</v>
+        <v>0.6869</v>
       </c>
     </row>
     <row r="47">
@@ -1037,10 +1037,10 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>23.82</v>
+        <v>23.67</v>
       </c>
       <c r="C47" t="n">
-        <v>0.7683</v>
+        <v>0.7585</v>
       </c>
     </row>
     <row r="48">
@@ -1050,10 +1050,10 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>22.31</v>
+        <v>22.11</v>
       </c>
       <c r="C48" t="n">
-        <v>0.7897</v>
+        <v>0.7766</v>
       </c>
     </row>
     <row r="49">
@@ -1063,10 +1063,10 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>20.79</v>
+        <v>20.46</v>
       </c>
       <c r="C49" t="n">
-        <v>0.8289</v>
+        <v>0.8198</v>
       </c>
     </row>
     <row r="50">
@@ -1076,10 +1076,10 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>23.86</v>
+        <v>23.46</v>
       </c>
       <c r="C50" t="n">
-        <v>0.763</v>
+        <v>0.7492</v>
       </c>
     </row>
     <row r="51">
@@ -1089,10 +1089,10 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>25.56</v>
+        <v>25.35</v>
       </c>
       <c r="C51" t="n">
-        <v>0.7832</v>
+        <v>0.7738</v>
       </c>
     </row>
     <row r="52">
@@ -1102,10 +1102,10 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>27.6</v>
+        <v>27.46</v>
       </c>
       <c r="C52" t="n">
-        <v>0.8532999999999999</v>
+        <v>0.8501</v>
       </c>
     </row>
     <row r="53">
@@ -1115,10 +1115,10 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>29.19</v>
+        <v>28.84</v>
       </c>
       <c r="C53" t="n">
-        <v>0.9124</v>
+        <v>0.9064</v>
       </c>
     </row>
     <row r="54">
@@ -1128,10 +1128,10 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>22.66</v>
+        <v>22.37</v>
       </c>
       <c r="C54" t="n">
-        <v>0.7403</v>
+        <v>0.7281</v>
       </c>
     </row>
     <row r="55">
@@ -1141,10 +1141,10 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>21.4</v>
+        <v>21.22</v>
       </c>
       <c r="C55" t="n">
-        <v>0.6634</v>
+        <v>0.6506</v>
       </c>
     </row>
     <row r="56">
@@ -1154,10 +1154,10 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>33.15</v>
+        <v>32.86</v>
       </c>
       <c r="C56" t="n">
-        <v>0.949</v>
+        <v>0.9444</v>
       </c>
     </row>
     <row r="57">
@@ -1167,10 +1167,10 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>25.27</v>
+        <v>25.08</v>
       </c>
       <c r="C57" t="n">
-        <v>0.7935</v>
+        <v>0.7853</v>
       </c>
     </row>
     <row r="58">
@@ -1180,10 +1180,10 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>31.41</v>
+        <v>30.9</v>
       </c>
       <c r="C58" t="n">
-        <v>0.9026999999999999</v>
+        <v>0.8958</v>
       </c>
     </row>
     <row r="59">
@@ -1193,10 +1193,10 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>26.25</v>
+        <v>25.96</v>
       </c>
       <c r="C59" t="n">
-        <v>0.8691</v>
+        <v>0.8615</v>
       </c>
     </row>
     <row r="60">
@@ -1206,10 +1206,10 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>22.59</v>
+        <v>22.05</v>
       </c>
       <c r="C60" t="n">
-        <v>0.7808</v>
+        <v>0.7619</v>
       </c>
     </row>
     <row r="61">
@@ -1219,10 +1219,10 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>22.72</v>
+        <v>22.58</v>
       </c>
       <c r="C61" t="n">
-        <v>0.5809</v>
+        <v>0.569</v>
       </c>
     </row>
     <row r="62">
@@ -1232,10 +1232,10 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>25.01</v>
+        <v>24.69</v>
       </c>
       <c r="C62" t="n">
-        <v>0.7702</v>
+        <v>0.7559</v>
       </c>
     </row>
     <row r="63">
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="B63" t="n">
-        <v>22.54</v>
+        <v>22.08</v>
       </c>
       <c r="C63" t="n">
-        <v>0.8357</v>
+        <v>0.8179</v>
       </c>
     </row>
     <row r="64">
@@ -1258,10 +1258,10 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>22.59</v>
+        <v>22.36</v>
       </c>
       <c r="C64" t="n">
-        <v>0.6245000000000001</v>
+        <v>0.6183999999999999</v>
       </c>
     </row>
     <row r="65">
@@ -1271,10 +1271,10 @@
         </is>
       </c>
       <c r="B65" t="n">
-        <v>26.9</v>
+        <v>26.73</v>
       </c>
       <c r="C65" t="n">
-        <v>0.7936</v>
+        <v>0.7884</v>
       </c>
     </row>
     <row r="66">
@@ -1284,10 +1284,10 @@
         </is>
       </c>
       <c r="B66" t="n">
-        <v>25.65</v>
+        <v>25.47</v>
       </c>
       <c r="C66" t="n">
-        <v>0.7371</v>
+        <v>0.7243000000000001</v>
       </c>
     </row>
     <row r="67">
@@ -1297,10 +1297,10 @@
         </is>
       </c>
       <c r="B67" t="n">
-        <v>22.35</v>
+        <v>22.3</v>
       </c>
       <c r="C67" t="n">
-        <v>0.6497000000000001</v>
+        <v>0.6455</v>
       </c>
     </row>
     <row r="68">
@@ -1310,10 +1310,10 @@
         </is>
       </c>
       <c r="B68" t="n">
-        <v>20.62</v>
+        <v>19.8</v>
       </c>
       <c r="C68" t="n">
-        <v>0.8917</v>
+        <v>0.8749</v>
       </c>
     </row>
     <row r="69">
@@ -1323,10 +1323,10 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>30.53</v>
+        <v>30.38</v>
       </c>
       <c r="C69" t="n">
-        <v>0.889</v>
+        <v>0.8855</v>
       </c>
     </row>
     <row r="70">
@@ -1336,10 +1336,10 @@
         </is>
       </c>
       <c r="B70" t="n">
-        <v>24.97</v>
+        <v>24.82</v>
       </c>
       <c r="C70" t="n">
-        <v>0.7612</v>
+        <v>0.7557</v>
       </c>
     </row>
     <row r="71">
@@ -1349,10 +1349,10 @@
         </is>
       </c>
       <c r="B71" t="n">
-        <v>22.25</v>
+        <v>22.15</v>
       </c>
       <c r="C71" t="n">
-        <v>0.6021</v>
+        <v>0.5959</v>
       </c>
     </row>
     <row r="72">
@@ -1362,10 +1362,10 @@
         </is>
       </c>
       <c r="B72" t="n">
-        <v>28.31</v>
+        <v>27.97</v>
       </c>
       <c r="C72" t="n">
-        <v>0.6804</v>
+        <v>0.6662</v>
       </c>
     </row>
     <row r="73">
@@ -1375,10 +1375,10 @@
         </is>
       </c>
       <c r="B73" t="n">
-        <v>20.64</v>
+        <v>20.22</v>
       </c>
       <c r="C73" t="n">
-        <v>0.8317</v>
+        <v>0.8188</v>
       </c>
     </row>
     <row r="74">
@@ -1388,10 +1388,10 @@
         </is>
       </c>
       <c r="B74" t="n">
-        <v>20.56</v>
+        <v>20.18</v>
       </c>
       <c r="C74" t="n">
-        <v>0.5924</v>
+        <v>0.5716</v>
       </c>
     </row>
     <row r="75">
@@ -1401,10 +1401,10 @@
         </is>
       </c>
       <c r="B75" t="n">
-        <v>24.14</v>
+        <v>23.73</v>
       </c>
       <c r="C75" t="n">
-        <v>0.7326</v>
+        <v>0.7004</v>
       </c>
     </row>
     <row r="76">
@@ -1414,10 +1414,10 @@
         </is>
       </c>
       <c r="B76" t="n">
-        <v>32.11</v>
+        <v>31.66</v>
       </c>
       <c r="C76" t="n">
-        <v>0.8902</v>
+        <v>0.8857</v>
       </c>
     </row>
     <row r="77">
@@ -1427,10 +1427,10 @@
         </is>
       </c>
       <c r="B77" t="n">
-        <v>23.62</v>
+        <v>22.6</v>
       </c>
       <c r="C77" t="n">
-        <v>0.7627</v>
+        <v>0.7209</v>
       </c>
     </row>
     <row r="78">
@@ -1440,10 +1440,10 @@
         </is>
       </c>
       <c r="B78" t="n">
-        <v>22.79</v>
+        <v>22.72</v>
       </c>
       <c r="C78" t="n">
-        <v>0.6795</v>
+        <v>0.675</v>
       </c>
     </row>
     <row r="79">
@@ -1453,10 +1453,10 @@
         </is>
       </c>
       <c r="B79" t="n">
-        <v>27.8</v>
+        <v>27.29</v>
       </c>
       <c r="C79" t="n">
-        <v>0.7839</v>
+        <v>0.7708</v>
       </c>
     </row>
     <row r="80">
@@ -1466,10 +1466,10 @@
         </is>
       </c>
       <c r="B80" t="n">
-        <v>25.65</v>
+        <v>25.45</v>
       </c>
       <c r="C80" t="n">
-        <v>0.7053</v>
+        <v>0.6967</v>
       </c>
     </row>
     <row r="81">
@@ -1479,10 +1479,10 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>35.74</v>
+        <v>35.57</v>
       </c>
       <c r="C81" t="n">
-        <v>0.954</v>
+        <v>0.9523</v>
       </c>
     </row>
     <row r="82">
@@ -1492,10 +1492,10 @@
         </is>
       </c>
       <c r="B82" t="n">
-        <v>37.7</v>
+        <v>37.21</v>
       </c>
       <c r="C82" t="n">
-        <v>0.9719</v>
+        <v>0.9693000000000001</v>
       </c>
     </row>
     <row r="83">
@@ -1505,10 +1505,10 @@
         </is>
       </c>
       <c r="B83" t="n">
-        <v>32.82</v>
+        <v>33.02</v>
       </c>
       <c r="C83" t="n">
-        <v>0.9409</v>
+        <v>0.9419</v>
       </c>
     </row>
     <row r="84">
@@ -1518,10 +1518,10 @@
         </is>
       </c>
       <c r="B84" t="n">
-        <v>22.49</v>
+        <v>22.27</v>
       </c>
       <c r="C84" t="n">
-        <v>0.7118</v>
+        <v>0.6995</v>
       </c>
     </row>
     <row r="85">
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="B85" t="n">
-        <v>28.96</v>
+        <v>28.77</v>
       </c>
       <c r="C85" t="n">
-        <v>0.8194</v>
+        <v>0.8136</v>
       </c>
     </row>
     <row r="86">
@@ -1544,10 +1544,10 @@
         </is>
       </c>
       <c r="B86" t="n">
-        <v>28.61</v>
+        <v>28.38</v>
       </c>
       <c r="C86" t="n">
-        <v>0.9071</v>
+        <v>0.9026999999999999</v>
       </c>
     </row>
     <row r="87">
@@ -1557,10 +1557,10 @@
         </is>
       </c>
       <c r="B87" t="n">
-        <v>30.61</v>
+        <v>30.45</v>
       </c>
       <c r="C87" t="n">
-        <v>0.8889</v>
+        <v>0.8856000000000001</v>
       </c>
     </row>
     <row r="88">
@@ -1570,10 +1570,10 @@
         </is>
       </c>
       <c r="B88" t="n">
-        <v>28.28</v>
+        <v>27.71</v>
       </c>
       <c r="C88" t="n">
-        <v>0.8923</v>
+        <v>0.8822</v>
       </c>
     </row>
     <row r="89">
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="B89" t="n">
-        <v>20.06</v>
+        <v>19.89</v>
       </c>
       <c r="C89" t="n">
-        <v>0.5814</v>
+        <v>0.5708</v>
       </c>
     </row>
     <row r="90">
@@ -1596,10 +1596,10 @@
         </is>
       </c>
       <c r="B90" t="n">
-        <v>26.9</v>
+        <v>26.77</v>
       </c>
       <c r="C90" t="n">
-        <v>0.7245</v>
+        <v>0.7167</v>
       </c>
     </row>
     <row r="91">
@@ -1609,10 +1609,10 @@
         </is>
       </c>
       <c r="B91" t="n">
-        <v>39.09</v>
+        <v>37.91</v>
       </c>
       <c r="C91" t="n">
-        <v>0.9782999999999999</v>
+        <v>0.9752999999999999</v>
       </c>
     </row>
     <row r="92">
@@ -1622,10 +1622,10 @@
         </is>
       </c>
       <c r="B92" t="n">
-        <v>24.19</v>
+        <v>24.02</v>
       </c>
       <c r="C92" t="n">
-        <v>0.6942</v>
+        <v>0.6830000000000001</v>
       </c>
     </row>
     <row r="93">
@@ -1635,10 +1635,10 @@
         </is>
       </c>
       <c r="B93" t="n">
-        <v>19.2</v>
+        <v>18.67</v>
       </c>
       <c r="C93" t="n">
-        <v>0.6679</v>
+        <v>0.6409</v>
       </c>
     </row>
     <row r="94">
@@ -1648,10 +1648,10 @@
         </is>
       </c>
       <c r="B94" t="n">
-        <v>28.68</v>
+        <v>28.23</v>
       </c>
       <c r="C94" t="n">
-        <v>0.9227</v>
+        <v>0.9196</v>
       </c>
     </row>
     <row r="95">
@@ -1661,10 +1661,10 @@
         </is>
       </c>
       <c r="B95" t="n">
-        <v>27.37</v>
+        <v>27.15</v>
       </c>
       <c r="C95" t="n">
-        <v>0.7905</v>
+        <v>0.7828000000000001</v>
       </c>
     </row>
     <row r="96">
@@ -1674,10 +1674,10 @@
         </is>
       </c>
       <c r="B96" t="n">
-        <v>20.33</v>
+        <v>20.16</v>
       </c>
       <c r="C96" t="n">
-        <v>0.4604</v>
+        <v>0.4446</v>
       </c>
     </row>
     <row r="97">
@@ -1687,10 +1687,10 @@
         </is>
       </c>
       <c r="B97" t="n">
-        <v>26.26</v>
+        <v>24.56</v>
       </c>
       <c r="C97" t="n">
-        <v>0.8836000000000001</v>
+        <v>0.8567</v>
       </c>
     </row>
     <row r="98">
@@ -1700,10 +1700,10 @@
         </is>
       </c>
       <c r="B98" t="n">
-        <v>25.13</v>
+        <v>24.92</v>
       </c>
       <c r="C98" t="n">
-        <v>0.7749</v>
+        <v>0.7634</v>
       </c>
     </row>
     <row r="99">
@@ -1713,10 +1713,10 @@
         </is>
       </c>
       <c r="B99" t="n">
-        <v>20.88</v>
+        <v>20.68</v>
       </c>
       <c r="C99" t="n">
-        <v>0.5465</v>
+        <v>0.5302</v>
       </c>
     </row>
     <row r="100">
@@ -1726,10 +1726,10 @@
         </is>
       </c>
       <c r="B100" t="n">
-        <v>26.17</v>
+        <v>25.62</v>
       </c>
       <c r="C100" t="n">
-        <v>0.8103</v>
+        <v>0.7902</v>
       </c>
     </row>
     <row r="101">
@@ -1739,10 +1739,10 @@
         </is>
       </c>
       <c r="B101" t="n">
-        <v>26.3</v>
+        <v>26.15</v>
       </c>
       <c r="C101" t="n">
-        <v>0.7487</v>
+        <v>0.7431</v>
       </c>
     </row>
     <row r="102">
@@ -1752,10 +1752,10 @@
         </is>
       </c>
       <c r="B102" t="n">
-        <v>26.34</v>
+        <v>26.02</v>
       </c>
       <c r="C102" t="n">
-        <v>0.7936</v>
+        <v>0.7834</v>
       </c>
     </row>
   </sheetData>
